--- a/eod_format.xlsx
+++ b/eod_format.xlsx
@@ -1,108 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2B5985E714F8F7697798391159D9483555E3FA9C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EOD Format" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EOD Format" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>task_id</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>ph_id</t>
-  </si>
-  <si>
-    <t>ph_name</t>
-  </si>
-  <si>
-    <t>department</t>
-  </si>
-  <si>
-    <t>weekly_intent_id</t>
-  </si>
-  <si>
-    <t>task_tier</t>
-  </si>
-  <si>
-    <t>tier_description</t>
-  </si>
-  <si>
-    <t>task_description</t>
-  </si>
-  <si>
-    <t>metric_name</t>
-  </si>
-  <si>
-    <t>metric_delta</t>
-  </si>
-  <si>
-    <t>hours_spent</t>
-  </si>
-  <si>
-    <t>verified</t>
-  </si>
-  <si>
-    <t>verification_url</t>
-  </si>
-  <si>
-    <t>waste_flag</t>
-  </si>
-  <si>
-    <t>waste_type</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>Web-03</t>
-  </si>
-  <si>
-    <t>Dilakshi</t>
-  </si>
-  <si>
-    <t>Website</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -136,24 +66,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -441,89 +430,847 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>task_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ph_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ph_name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weekly_intent_id</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>task_tier</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tier_description</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>task_description</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>metric_name</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>metric_delta</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>hours_spent</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>verification_url</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>waste_flag</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>waste_type</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Web-03</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dilakshi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Shipped / Live output</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Last Piece Collection page shipped live: scarcity count display, badge, copy-code button, top-bar navigation</t>
+        </is>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Live collection page updates (Ledsone)</t>
+        </is>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Shipped / Live output</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ledsone.us homepage new products section published live</t>
+        </is>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Live homepage update confirmed</t>
+        </is>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Moderate impact</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EOD dashboard developed and deployed (dev-complete, testing deferred to next day)</t>
+        </is>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Deployment noted in EOD 2026-04-02</t>
+        </is>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-004</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Moderate impact</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Blog tool bug fixed twice across the week — functionality confirmed restored</t>
+        </is>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Bug fix applied (2026-04-01, 2026-04-03)</t>
+        </is>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-005</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Shipped / Live output</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Banner updates pushed live across four stores: DC Voltage, Ledsone.de, Vintage Lite, Ledsone.fr</t>
+        </is>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Live banner updates confirmed (2026-04-01, 2026-04-02)</t>
+        </is>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-006</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Shipped / Live output</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ledsone.de collection colour changes pushed live</t>
+        </is>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Live UI update confirmed (2026-04-02)</t>
+        </is>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-007</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Low / No verifiable output</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Claude + Clarity workflow for Meta Ads URL analysis: 2h consumed, no shipped report, no confirmed recipient in ads team</t>
+        </is>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-008</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Low / No verifiable output</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Refund/return sheet matching (3h): internal data hygiene with no verified downstream impact on any report or decision</t>
+        </is>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-009</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Low / No verifiable output</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Discount variant picker: 4.5h spent Thu+Fri without shipping — feature entered without pre-mapped logic, repeated debugging loops</t>
+        </is>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-010</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Low / No verifiable output</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Configurator testing + three follow-up discussions across Tue/Wed/Thu — no fix deployed, no timeline confirmed</t>
+        </is>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-011</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Low / No verifiable output</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Messaging app analysis (2h): concluded with decisions pending, no final selection, no forcing function set</t>
+        </is>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-012</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Low / No verifiable output</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>EOD dashboard shipped Thursday but testing not completed Friday — deployed-but-unvalidated signals incomplete ownership of delivery cycle</t>
+        </is>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Career</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Low / No verifiable output</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Three consecutive configurator discussions without owning the resolution — pattern shows low accountability on cross-functional blockers</t>
+        </is>
+      </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Career</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TECH-02-2026-04-03-014</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TECH-02</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Kuberan</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Low / No verifiable output</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Discount variant picker started without finalized approach — explicitly logged: debugging without a finalized approach is a repeatable skill gap</t>
+        </is>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Career</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,B,C,D,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A | Revenue-Direct,B | Revenue-Support,C | Operational Necessity,D | Administrative / Low-Value,S | Strategic / High-Impact"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ACOS_REDUCTION,CTR,CVR,Impressions,LISTING_PERFORMANCE,Margin,Rank,RETURN_RATE,Revenue,ROAS,SALES_UPLIFT"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="O2:O1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="M2:M1048576" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,1,TRUE,FALSE,true,false"</formula1>
     </dataValidation>
   </dataValidations>
